--- a/sheets/대금율보/검수/삼귀의.xlsx
+++ b/sheets/대금율보/검수/삼귀의.xlsx
@@ -2253,18 +2253,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.67" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.67" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.67" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.67" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -2385,7 +2385,7 @@
       <c r="F6" s="21"/>
       <c r="G6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.67" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.67" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.67" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.67" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.67" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="G11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.67" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.67" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.67" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.67" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.67" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.67" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2718,7 +2718,7 @@
       <c r="F17" s="21"/>
       <c r="G17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.67" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -2727,7 +2727,7 @@
       <c r="F18" s="21"/>
       <c r="G18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.67" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -2754,6 +2754,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="73"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>